--- a/data/testdata.xlsx
+++ b/data/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BLaptop\TCS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466A50D1-FF32-4C34-9DE5-7FB20D2BF6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B634C922-BA14-4C0D-ACBF-C99DF7B52D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2DE02770-E7DF-4C29-9495-8C2A8106DF1C}"/>
   </bookViews>
@@ -48,10 +48,10 @@
     <t>admin123</t>
   </si>
   <si>
-    <t>wronguser</t>
-  </si>
-  <si>
-    <t>wrongpassword</t>
+    <t>exceluser</t>
+  </si>
+  <si>
+    <t>excelpwd</t>
   </si>
 </sst>
 </file>
